--- a/examples/HO_SO_CONG_HOP_TUYEN_A5/HO_SO_THUC_CHIEN_HUB_AND_SPOKE_CONG_A5/GOI_D_QS_DU_TOAN_THANH_TOAN/08_Du_Toan_GXD_Thong_Tu_11_2021_Cong_A5.xlsx
+++ b/examples/HO_SO_CONG_HOP_TUYEN_A5/HO_SO_THUC_CHIEN_HUB_AND_SPOKE_CONG_A5/GOI_D_QS_DU_TOAN_THANH_TOAN/08_Du_Toan_GXD_Thong_Tu_11_2021_Cong_A5.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,8 +48,11 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -60,8 +65,13 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -83,11 +93,25 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,6 +119,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -460,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,9 +545,8 @@
           <t>T = Vật liệu + Nhân công + Máy thi công</t>
         </is>
       </c>
-      <c r="D5" s="3">
-        <f>42500000000</f>
-        <v/>
+      <c r="D5" s="5" t="n">
+        <v>42500000000</v>
       </c>
       <c r="E5" s="3">
         <f>D5/$D$10</f>
@@ -528,7 +554,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Khối lượng x Đơn giá TT 12</t>
+          <t>ĐẦU VÀO: nhập từ dự toán chi tiết đã duyệt (Σ khối lượng × đơn giá theo định mức). CHƯA liên kết với khối lượng/đơn giá trong hồ sơ này</t>
         </is>
       </c>
     </row>
@@ -545,11 +571,11 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>GT = Chi phí chung (7.3%) + Nhà tạm (1.2%)</t>
+          <t>GT = T × (chi phí chung + nhà tạm)</t>
         </is>
       </c>
       <c r="D6" s="3">
-        <f>D5*0.085</f>
+        <f>D5*(D13+D14)</f>
         <v/>
       </c>
       <c r="E6" s="3">
@@ -558,7 +584,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>8.5% x Chi phí trực tiếp T</t>
+          <t>Theo ô tỷ lệ D13 + D14</t>
         </is>
       </c>
     </row>
@@ -575,11 +601,11 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>TL = 5.5% x (T + GT)</t>
+          <t>TL = (T + GT) × tỷ lệ TL</t>
         </is>
       </c>
       <c r="D7" s="3">
-        <f>(D5+D6)*0.055</f>
+        <f>(D5+D6)*D15</f>
         <v/>
       </c>
       <c r="E7" s="3">
@@ -588,7 +614,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>5.5% x (T + GT)</t>
+          <t>Theo ô tỷ lệ D15</t>
         </is>
       </c>
     </row>
@@ -635,11 +661,11 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>VAT = 10% x G</t>
+          <t>VAT = G × thuế suất</t>
         </is>
       </c>
       <c r="D9" s="3">
-        <f>D8*0.10</f>
+        <f>D8*D16</f>
         <v/>
       </c>
       <c r="E9" s="3">
@@ -648,7 +674,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Thuế suất VAT 10%</t>
+          <t>Theo ô tỷ lệ D16</t>
         </is>
       </c>
     </row>
@@ -681,6 +707,53 @@
         <is>
           <t>GIÁ TRỊ DỰ TOÁN PHÊ DUYỆT</t>
         </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>TỶ LỆ ĐẦU VÀO (đổi ô vàng, các dòng II-VI tự tính lại)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Chi phí chung (% T)</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>0.073</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nhà tạm để ở và điều hành thi công (% T)</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Thu nhập chịu thuế tính trước (% (T + GT))</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Thuế giá trị gia tăng (% G)</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
